--- a/public/inputs/y01-global-perspectives - input.xlsx
+++ b/public/inputs/y01-global-perspectives - input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,9 +441,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1 · Values and Beliefs</t>
-        </is>
-      </c>
+          <t>Unit 1 · Sports and recreation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -453,9 +454,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What are values?</t>
-        </is>
-      </c>
+          <t>1.1 My favourite sport and game</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -465,9 +467,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>My values</t>
-        </is>
-      </c>
+          <t>1.2 Indoor and outdoor games</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -477,9 +480,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What are beliefs?</t>
-        </is>
-      </c>
+          <t>1.3 Traditional games around the world</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,9 +493,10 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beliefs around us</t>
-        </is>
-      </c>
+          <t>1.4 Why do we exercise?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -501,9 +506,10 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Respect</t>
-        </is>
-      </c>
+          <t>1.5 Playing safely</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -513,9 +519,10 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fairness</t>
-        </is>
-      </c>
+          <t>1.6 Teamwork in sports</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -525,9 +532,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Different but same</t>
-        </is>
-      </c>
+          <t>1.7 Sports in our community</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -537,9 +545,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caring &amp; helping</t>
-        </is>
-      </c>
+          <t>1.8 Different people, different sports</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -549,21 +558,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9–10. Review Project: Class Values Boo</t>
-        </is>
-      </c>
+          <t>1.9 Recreation and free time</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unit 2 · Looking After the Planet</t>
-        </is>
-      </c>
+          <t>1.10 Weather and sport</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -573,21 +584,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Our Planet</t>
-        </is>
-      </c>
+          <t>1.11 Healthy habits through sport</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What I love about Earth</t>
-        </is>
-      </c>
+          <t>Unit 2 · Rich and poor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -597,9 +610,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reduce – Saving energy</t>
-        </is>
-      </c>
+          <t>2.1 What do we need to live?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -609,9 +623,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reduce role-play</t>
-        </is>
-      </c>
+          <t>2.2 Needs and wants</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -621,9 +636,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reuse</t>
-        </is>
-      </c>
+          <t>2.3 Different homes around the world</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -633,9 +649,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recycle – Sorting</t>
-        </is>
-      </c>
+          <t>2.4 Jobs and helping families</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -645,9 +662,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pollution – Demo (clean vs dirty water)</t>
-        </is>
-      </c>
+          <t>2.5 Communities helping together</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -657,33 +675,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>How I can help</t>
-        </is>
-      </c>
+          <t>2.6 Saving and spending wisely</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19–20. Review Project: Planet Pledge</t>
-        </is>
-      </c>
+          <t>Unit 3 · Digital world</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unit 3 · Water, Food &amp; Farming</t>
-        </is>
-      </c>
+          <t>3.1 What is the digital world?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -693,9 +714,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Why water is important</t>
-        </is>
-      </c>
+          <t>3.2 Digital devices around us</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -705,9 +727,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Where water comes from</t>
-        </is>
-      </c>
+          <t>3.3 Technology around the world</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -717,9 +740,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why food is important</t>
-        </is>
-      </c>
+          <t>3.4 Learning with technology</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -729,9 +753,10 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Food journey (farm to plate)</t>
-        </is>
-      </c>
+          <t>3.5 Staying safe online</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -741,9 +766,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Farming – Animals</t>
-        </is>
-      </c>
+          <t>3.6 Being kind online</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -753,9 +779,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Farming – Plants</t>
-        </is>
-      </c>
+          <t>3.7 Screen time control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -765,21 +792,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Food around the world</t>
-        </is>
-      </c>
+          <t>3.8 Designing the technology of the future</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>How we waste food</t>
-        </is>
-      </c>
+          <t>Unit 4 · Improving communication</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -789,21 +818,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29–30. Review Project: Thank You Farmers Book</t>
-        </is>
-      </c>
+          <t>4.1 What is communication?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unit 4 · Health &amp; Wellbeing</t>
-        </is>
-      </c>
+          <t>4.2 Speaking and listening</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -813,9 +844,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is health?</t>
-        </is>
-      </c>
+          <t>4.3 Verbal and non-verbal communication</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -825,9 +857,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Exercise</t>
-        </is>
-      </c>
+          <t>4.4 Feelings and communication</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -837,9 +870,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Food &amp; health – Balanced plate</t>
-        </is>
-      </c>
+          <t>4.5. Communication around the world</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -849,9 +883,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Healthy lunchbox</t>
-        </is>
-      </c>
+          <t>4.6 Solving problems through communication</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -861,21 +896,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hygiene – Glitter germs experiment</t>
-        </is>
-      </c>
+          <t>4.7 Digital communication</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hygiene routine</t>
-        </is>
-      </c>
+          <t>Unit 5 · Moving goods and people</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -885,9 +922,10 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Feelings &amp; wellbeing</t>
-        </is>
-      </c>
+          <t>5.1 Ways to travel</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -897,9 +935,10 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kindness</t>
-        </is>
-      </c>
+          <t>5.2 Moving goods</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -909,21 +948,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>39–40. Review Project: My Healthy Life Poster</t>
-        </is>
-      </c>
+          <t>5.3 Land, water and air transport</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Unit 5 · Family, Friends, Community &amp; Culture</t>
-        </is>
-      </c>
+          <t>5.4 Safe travel</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -933,9 +974,10 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is family?</t>
-        </is>
-      </c>
+          <t>5.5 Transport around the world</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -945,9 +987,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>My family</t>
-        </is>
-      </c>
+          <t>5.6 Helping the environment</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -957,9 +1000,10 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Friends</t>
-        </is>
-      </c>
+          <t>5.7 Community helpers and transport</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -969,21 +1013,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Why friends matter</t>
-        </is>
-      </c>
+          <t>5.8 Design future transport</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>My community</t>
-        </is>
-      </c>
+          <t>Unit 6 · Family, friends, community and culture</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -993,9 +1039,10 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Community helpers</t>
-        </is>
-      </c>
+          <t>6.1 My family</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1005,9 +1052,10 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Culture – Festivals</t>
-        </is>
-      </c>
+          <t>6.2 Different families around the world</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1017,9 +1065,10 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Traditions</t>
-        </is>
-      </c>
+          <t>6.3 Being a good friend</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1029,9 +1078,10 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Working together</t>
-        </is>
-      </c>
+          <t>6.4 Our school and local community</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1041,9 +1091,10 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
+          <t>6.5 Working together to build a caring community</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1053,9 +1104,218 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>51–52. Review Project: Celebration Presentation</t>
-        </is>
-      </c>
+          <t>6.6 Celebrations and traditions</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6.7 Respecting different cultures</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Term 1 Revision</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Term 1 Assessment</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Term 1 School Activities</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Term 2 Revision</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Term 2 Assessment</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Term 2 School Activities</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Term 3 Revision</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Term 3 Assessment</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Term 3 School Activities</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unit 1 Humanities</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unit 2 Humanities</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unit 3 Humanities</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unit 4 Humanities</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unit 5 Humanities</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unit 6 Humanities</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
